--- a/Result/profitability/6112.xlsx
+++ b/Result/profitability/6112.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>0.27125</v>
+        <v>0.45375</v>
       </c>
       <c r="N2" t="n">
-        <v>13.68</v>
+        <v>13.615</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30375</v>
+        <v>0.59375</v>
       </c>
       <c r="N3" t="n">
-        <v>13.05625</v>
+        <v>13.4025</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42125</v>
+        <v>0.59375</v>
       </c>
       <c r="N4" t="n">
-        <v>12.915</v>
+        <v>12.98</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.38875</v>
+        <v>0.5825</v>
       </c>
       <c r="N5" t="n">
-        <v>12.30375</v>
+        <v>12.5475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4025</v>
+        <v>0.51625</v>
       </c>
       <c r="N6" t="n">
         <v>12.23625</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3425</v>
+        <v>0.47625</v>
       </c>
       <c r="N7" t="n">
-        <v>11.83</v>
+        <v>11.715</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31125</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>11.14125</v>
+        <v>11.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6552</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5581</v>
+      </c>
+      <c r="E75" t="n">
+        <v>971</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>289</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>104</v>
+      </c>
+      <c r="J75" t="n">
+        <v>393</v>
+      </c>
+      <c r="K75" t="n">
+        <v>316</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.22625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8.882352941176469</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9500000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06849315068493156</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>11.92307692307692</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.950000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1515151515151516</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
